--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5683440</v>
+        <v>6331.55</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>69991040</v>
+        <v>77972.47</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6932083.2</v>
+        <v>7722.58</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4641000</v>
+        <v>5170.24</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2211124.72</v>
+        <v>2463.27</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>25529742.35</v>
+        <v>28441.03</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5141226.02</v>
+        <v>5727.51</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4133454.29</v>
+        <v>4604.81</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6531648.2</v>
+        <v>7276.48</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6747300</v>
+        <v>7516.73</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4535804</v>
+        <v>5053.04</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25513600</v>
+        <v>28423.04</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>13609554</v>
+        <v>15161.52</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6084470</v>
+        <v>6778.31</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>30258011</v>
+        <v>33708.48</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>50801457</v>
+        <v>56594.6</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>33119318.4</v>
+        <v>36896.08</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4675933.64</v>
+        <v>5209.15</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2900625</v>
+        <v>3231.4</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2560499.2</v>
+        <v>2852.49</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5683440</v>
+        <v>6331.55</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2803759</v>
+        <v>3123.49</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>69406363.25</v>
+        <v>77321.11</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2211124.72</v>
+        <v>2463.27</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5712000</v>
+        <v>6363.37</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3237444.98</v>
+        <v>3606.63</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3237444.98</v>
+        <v>3606.63</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3237444.98</v>
+        <v>3606.63</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3237444.98</v>
+        <v>3606.63</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3237444.98</v>
+        <v>3606.63</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6474889.96</v>
+        <v>7213.25</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2810304</v>
+        <v>3130.78</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2175711.51</v>
+        <v>2423.82</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>68011942.67</v>
+        <v>75767.67999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>9376496.710000001</v>
+        <v>10445.75</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3237444.98</v>
+        <v>3606.63</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3263309.63</v>
+        <v>3635.44</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3877020</v>
+        <v>4319.14</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>21545664</v>
+        <v>24002.62</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2486505</v>
+        <v>2770.05</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>42054742.8</v>
+        <v>46850.45</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>32518862.25</v>
+        <v>36227.15</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>23827736.52</v>
+        <v>26544.93</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>6500798.64</v>
+        <v>7242.12</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2399903.94</v>
+        <v>2673.58</v>
       </c>
     </row>
   </sheetData>
